--- a/rebuttal/tables/rebuttal_results_simple_previous.xlsx
+++ b/rebuttal/tables/rebuttal_results_simple_previous.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,16 +49,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -72,7 +62,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -81,12 +71,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -683,9 +667,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>0.8816 ± 0.0026</t>
         </is>
       </c>
     </row>
@@ -715,9 +699,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>0.8812 ± 0.0038</t>
         </is>
       </c>
     </row>
@@ -779,9 +763,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>0.8923 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -811,9 +795,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>0.8923 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -875,9 +859,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>0.8914 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -907,9 +891,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>0.8914 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -971,9 +955,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>0.8938 ± 0.0015</t>
         </is>
       </c>
     </row>
@@ -1003,9 +987,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>0.8938 ± 0.0015</t>
         </is>
       </c>
     </row>
@@ -1067,9 +1051,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>0.8816 ± 0.0030</t>
         </is>
       </c>
     </row>
@@ -1099,9 +1083,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>0.8812 ± 0.0033</t>
         </is>
       </c>
     </row>
@@ -1131,9 +1115,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>0.8800 ± 0.0040</t>
         </is>
       </c>
     </row>
@@ -1195,9 +1179,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>0.8914 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -1227,9 +1211,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0.8914 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -1259,9 +1243,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>0.8914 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -1419,9 +1403,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>0.8936</t>
         </is>
       </c>
     </row>
@@ -1451,9 +1435,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>0.8936</t>
         </is>
       </c>
     </row>
@@ -1483,9 +1467,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>0.9004</t>
         </is>
       </c>
     </row>
@@ -1515,9 +1499,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>0.9004</t>
         </is>
       </c>
     </row>
@@ -1547,9 +1531,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>0.9004</t>
         </is>
       </c>
     </row>
@@ -1579,9 +1563,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>0.8827</t>
         </is>
       </c>
     </row>
@@ -1611,9 +1595,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>0.8840</t>
         </is>
       </c>
     </row>
@@ -1643,9 +1627,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>0.8443</t>
         </is>
       </c>
     </row>
@@ -1675,9 +1659,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>0.8475</t>
         </is>
       </c>
     </row>
@@ -1707,9 +1691,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>0.8936</t>
         </is>
       </c>
     </row>
@@ -1739,9 +1723,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>0.8936</t>
         </is>
       </c>
     </row>
@@ -1771,9 +1755,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>0.9004</t>
         </is>
       </c>
     </row>
@@ -1803,9 +1787,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>0.9004</t>
         </is>
       </c>
     </row>
@@ -1835,9 +1819,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>0.9004</t>
         </is>
       </c>
     </row>
@@ -1867,9 +1851,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>0.8827</t>
         </is>
       </c>
     </row>
@@ -1899,9 +1883,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>0.8840</t>
         </is>
       </c>
     </row>
@@ -1931,9 +1915,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>0.8443</t>
         </is>
       </c>
     </row>
@@ -1963,9 +1947,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>0.8475</t>
         </is>
       </c>
     </row>
@@ -2155,9 +2139,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>0.8938 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -2187,9 +2171,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>0.8938 ± 0.0015</t>
         </is>
       </c>
     </row>
@@ -2219,9 +2203,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>0.8938 ± 0.0015</t>
         </is>
       </c>
     </row>
@@ -2251,9 +2235,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>0.8938 ± 0.0015</t>
         </is>
       </c>
     </row>
@@ -2283,9 +2267,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>0.8945 ± 0.0016</t>
         </is>
       </c>
     </row>
@@ -2443,9 +2427,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>0.8917 ± 0.0011</t>
         </is>
       </c>
     </row>
@@ -2475,9 +2459,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>0.8923 ± 0.0008</t>
         </is>
       </c>
     </row>
@@ -2507,9 +2491,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>0.8926 ± 0.0005</t>
         </is>
       </c>
     </row>
@@ -2539,9 +2523,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>0.8997 ± 0.0008</t>
         </is>
       </c>
     </row>
@@ -2571,9 +2555,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>0.8954 ± 0.0013</t>
         </is>
       </c>
     </row>
@@ -2603,9 +2587,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>0.8743 ± 0.0219</t>
         </is>
       </c>
     </row>
@@ -2635,9 +2619,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>0.8721 ± 0.0154</t>
         </is>
       </c>
     </row>
@@ -2667,9 +2651,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>0.8657 ± 0.0172</t>
         </is>
       </c>
     </row>
@@ -2699,9 +2683,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -2731,9 +2715,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0133</t>
         </is>
       </c>
     </row>
@@ -2763,9 +2747,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>0.8765 ± 0.0136</t>
         </is>
       </c>
     </row>
@@ -2795,9 +2779,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>0.8758 ± 0.0151</t>
         </is>
       </c>
     </row>
@@ -2827,9 +2811,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -2859,9 +2843,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>0.8765 ± 0.0136</t>
         </is>
       </c>
     </row>
@@ -2891,9 +2875,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>0.8758 ± 0.0151</t>
         </is>
       </c>
     </row>
@@ -2923,9 +2907,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -2955,9 +2939,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>0.8773 ± 0.0143</t>
         </is>
       </c>
     </row>
@@ -2987,9 +2971,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>0.8762 ± 0.0155</t>
         </is>
       </c>
     </row>
@@ -3019,9 +3003,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>0.8765</t>
         </is>
       </c>
     </row>
@@ -3051,9 +3035,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>0.8765</t>
         </is>
       </c>
     </row>
@@ -3083,9 +3067,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>0.8833</t>
         </is>
       </c>
     </row>
@@ -3115,9 +3099,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>0.8844</t>
         </is>
       </c>
     </row>
@@ -3147,9 +3131,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>0.8844</t>
         </is>
       </c>
     </row>
@@ -3179,9 +3163,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>0.8777</t>
         </is>
       </c>
     </row>
@@ -3211,9 +3195,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>0.8799</t>
         </is>
       </c>
     </row>
@@ -3243,9 +3227,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>0.8563</t>
         </is>
       </c>
     </row>
@@ -3275,9 +3259,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>0.8316</t>
         </is>
       </c>
     </row>
@@ -3307,9 +3291,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>0.8765</t>
         </is>
       </c>
     </row>
@@ -3339,9 +3323,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>0.8765</t>
         </is>
       </c>
     </row>
@@ -3371,9 +3355,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>0.8833</t>
         </is>
       </c>
     </row>
@@ -3403,9 +3387,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>0.8844</t>
         </is>
       </c>
     </row>
@@ -3435,9 +3419,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>0.8844</t>
         </is>
       </c>
     </row>
@@ -3467,9 +3451,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>0.8777</t>
         </is>
       </c>
     </row>
@@ -3499,9 +3483,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>0.8799</t>
         </is>
       </c>
     </row>
@@ -3531,9 +3515,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>0.8563</t>
         </is>
       </c>
     </row>
@@ -3563,9 +3547,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>0.8316</t>
         </is>
       </c>
     </row>
@@ -3595,9 +3579,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3627,9 +3611,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3659,9 +3643,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3691,9 +3675,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3723,9 +3707,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3755,9 +3739,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3787,9 +3771,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3819,9 +3803,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3851,9 +3835,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -3883,9 +3867,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>0.8728 ± 0.0162</t>
         </is>
       </c>
     </row>
@@ -3915,9 +3899,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>0.1422 ± 0.0653</t>
         </is>
       </c>
     </row>
@@ -3947,9 +3931,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>0.8657 ± 0.0234</t>
         </is>
       </c>
     </row>
@@ -3979,9 +3963,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -4011,9 +3995,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>0.8750 ± 0.0124</t>
         </is>
       </c>
     </row>
@@ -4043,9 +4027,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>0.9001 ± 0.0092</t>
         </is>
       </c>
     </row>
@@ -4075,9 +4059,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>0.8765 ± 0.0062</t>
         </is>
       </c>
     </row>
@@ -4107,9 +4091,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>0.8668 ± 0.0080</t>
         </is>
       </c>
     </row>
@@ -4139,9 +4123,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>0.8634 ± 0.0226</t>
         </is>
       </c>
     </row>
@@ -4171,9 +4155,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>0.8754 ± 0.0108</t>
         </is>
       </c>
     </row>
@@ -4203,9 +4187,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>0.7627 ± 0.0114</t>
         </is>
       </c>
     </row>
@@ -4235,9 +4219,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>0.7749 ± 0.0054</t>
         </is>
       </c>
     </row>
@@ -4267,9 +4251,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>0.7745 ± 0.0070</t>
         </is>
       </c>
     </row>
@@ -4299,9 +4283,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -4331,9 +4315,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>0.7711 ± 0.0067</t>
         </is>
       </c>
     </row>
@@ -4363,9 +4347,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>0.7769 ± 0.0051</t>
         </is>
       </c>
     </row>
@@ -4395,9 +4379,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>0.7692 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -4427,9 +4411,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>0.7713 ± 0.0055</t>
         </is>
       </c>
     </row>
@@ -4459,9 +4443,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>0.7771 ± 0.0043</t>
         </is>
       </c>
     </row>
@@ -4491,9 +4475,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>0.7693 ± 0.0057</t>
         </is>
       </c>
     </row>
@@ -4523,9 +4507,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -4555,9 +4539,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>0.7772 ± 0.0040</t>
         </is>
       </c>
     </row>
@@ -4587,9 +4571,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>0.7695 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -4619,9 +4603,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>0.7745</t>
         </is>
       </c>
     </row>
@@ -4651,9 +4635,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>0.7745</t>
         </is>
       </c>
     </row>
@@ -4683,9 +4667,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>0.7745</t>
         </is>
       </c>
     </row>
@@ -4715,9 +4699,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>0.7749</t>
         </is>
       </c>
     </row>
@@ -4747,9 +4731,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>0.7748</t>
         </is>
       </c>
     </row>
@@ -4779,9 +4763,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>0.6869</t>
         </is>
       </c>
     </row>
@@ -4811,9 +4795,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>0.6876</t>
         </is>
       </c>
     </row>
@@ -4843,9 +4827,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>0.6481</t>
         </is>
       </c>
     </row>
@@ -4875,9 +4859,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>0.5424</t>
         </is>
       </c>
     </row>
@@ -4907,9 +4891,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>0.7745</t>
         </is>
       </c>
     </row>
@@ -4939,9 +4923,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>0.7745</t>
         </is>
       </c>
     </row>
@@ -4971,9 +4955,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>0.7745</t>
         </is>
       </c>
     </row>
@@ -5003,9 +4987,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>0.7749</t>
         </is>
       </c>
     </row>
@@ -5035,9 +5019,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>0.7748</t>
         </is>
       </c>
     </row>
@@ -5067,9 +5051,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>0.6869</t>
         </is>
       </c>
     </row>
@@ -5099,9 +5083,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>0.6876</t>
         </is>
       </c>
     </row>
@@ -5131,9 +5115,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>0.6481</t>
         </is>
       </c>
     </row>
@@ -5163,9 +5147,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>0.5424</t>
         </is>
       </c>
     </row>
@@ -5195,9 +5179,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -5227,9 +5211,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>0.7716 ± 0.0055</t>
         </is>
       </c>
     </row>
@@ -5259,9 +5243,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>0.7714 ± 0.0055</t>
         </is>
       </c>
     </row>
@@ -5291,9 +5275,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>0.7716 ± 0.0055</t>
         </is>
       </c>
     </row>
@@ -5323,9 +5307,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -5355,9 +5339,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0056</t>
         </is>
       </c>
     </row>
@@ -5387,9 +5371,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0056</t>
         </is>
       </c>
     </row>
@@ -5419,9 +5403,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>0.7716 ± 0.0055</t>
         </is>
       </c>
     </row>
@@ -5451,9 +5435,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>0.7716 ± 0.0054</t>
         </is>
       </c>
     </row>
@@ -5483,9 +5467,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>0.7681 ± 0.0105</t>
         </is>
       </c>
     </row>
@@ -5515,9 +5499,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>0.6422 ± 0.0427</t>
         </is>
       </c>
     </row>
@@ -5547,9 +5531,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>0.7651 ± 0.0087</t>
         </is>
       </c>
     </row>
@@ -5579,9 +5563,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -5611,9 +5595,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>0.7715 ± 0.0059</t>
         </is>
       </c>
     </row>
@@ -5643,9 +5627,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>0.7591 ± 0.0156</t>
         </is>
       </c>
     </row>
@@ -5675,9 +5659,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>0.7654 ± 0.0086</t>
         </is>
       </c>
     </row>
@@ -5707,9 +5691,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>0.7668 ± 0.0105</t>
         </is>
       </c>
     </row>
@@ -5739,9 +5723,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>0.7650 ± 0.0096</t>
         </is>
       </c>
     </row>
@@ -5771,9 +5755,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>0.7697 ± 0.0072</t>
         </is>
       </c>
     </row>
@@ -5931,9 +5915,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>0.9084</t>
         </is>
       </c>
     </row>
@@ -5963,9 +5947,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>0.9083</t>
         </is>
       </c>
     </row>
@@ -5995,9 +5979,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>0.9745</t>
         </is>
       </c>
     </row>
@@ -6027,9 +6011,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>0.9745</t>
         </is>
       </c>
     </row>
@@ -6059,9 +6043,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>0.9745</t>
         </is>
       </c>
     </row>
@@ -6091,9 +6075,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>0.9903</t>
         </is>
       </c>
     </row>
@@ -6123,9 +6107,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>0.9903</t>
         </is>
       </c>
     </row>
@@ -6155,9 +6139,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>0.9921</t>
         </is>
       </c>
     </row>
@@ -6187,9 +6171,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>0.6568</t>
         </is>
       </c>
     </row>
@@ -6219,9 +6203,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>0.9084</t>
         </is>
       </c>
     </row>
@@ -6251,9 +6235,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>0.9083</t>
         </is>
       </c>
     </row>
@@ -6283,9 +6267,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>0.9745</t>
         </is>
       </c>
     </row>
@@ -6315,9 +6299,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F183" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>0.9745</t>
         </is>
       </c>
     </row>
@@ -6347,9 +6331,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F184" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>0.9745</t>
         </is>
       </c>
     </row>
@@ -6379,9 +6363,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>0.9903</t>
         </is>
       </c>
     </row>
@@ -6411,9 +6395,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>0.9903</t>
         </is>
       </c>
     </row>
@@ -6443,9 +6427,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F187" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>0.9921</t>
         </is>
       </c>
     </row>
@@ -6475,9 +6459,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F188" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>0.6568</t>
         </is>
       </c>
     </row>
@@ -6667,9 +6651,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F194" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>0.9217 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -6699,9 +6683,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>0.9217 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -6731,9 +6715,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>0.9217 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -6763,9 +6747,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>0.9217 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -6795,9 +6779,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>0.9207 ± 0.0086</t>
         </is>
       </c>
     </row>
@@ -6955,9 +6939,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F203" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>0.9398 ± 0.0040</t>
         </is>
       </c>
     </row>
@@ -6987,9 +6971,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F204" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>0.8971 ± 0.0215</t>
         </is>
       </c>
     </row>
@@ -7019,9 +7003,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>0.9104 ± 0.0077</t>
         </is>
       </c>
     </row>
@@ -7051,9 +7035,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F206" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>0.9661 ± 0.0023</t>
         </is>
       </c>
     </row>
@@ -7083,9 +7067,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>0.9337 ± 0.0041</t>
         </is>
       </c>
     </row>
@@ -7115,9 +7099,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>运行中（0/3）</t>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>0.9633 ± 0.0028</t>
         </is>
       </c>
     </row>
@@ -7147,9 +7131,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9493（1/3）</t>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>0.9544 ± 0.0046</t>
         </is>
       </c>
     </row>
@@ -7179,9 +7163,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9457（1/3）</t>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>0.9511 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7211,9 +7195,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -7243,9 +7227,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>运行中（0/3）</t>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>0.9633 ± 0.0028</t>
         </is>
       </c>
     </row>
@@ -7275,9 +7259,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>0.9635 ± 0.0028</t>
         </is>
       </c>
     </row>
@@ -7307,9 +7291,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>0.9634 ± 0.0027</t>
         </is>
       </c>
     </row>
@@ -7339,9 +7323,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9493（1/3）</t>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>0.9544 ± 0.0046</t>
         </is>
       </c>
     </row>
@@ -7371,9 +7355,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F216" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>0.9545 ± 0.0046</t>
         </is>
       </c>
     </row>
@@ -7403,9 +7387,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F217" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>0.9545 ± 0.0045</t>
         </is>
       </c>
     </row>
@@ -7435,9 +7419,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F218" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9457（1/3）</t>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>0.9511 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7467,9 +7451,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F219" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>0.9511 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7499,9 +7483,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F220" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>0.9511 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7531,9 +7515,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F221" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -7563,9 +7547,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F222" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -7595,9 +7579,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F223" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -7627,9 +7611,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>运行中（0/3）</t>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>0.9633 ± 0.0028</t>
         </is>
       </c>
     </row>
@@ -7659,9 +7643,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>0.9636 ± 0.0023</t>
         </is>
       </c>
     </row>
@@ -7691,9 +7675,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>0.9638 ± 0.0025</t>
         </is>
       </c>
     </row>
@@ -7723,9 +7707,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F227" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>0.9634 ± 0.0022</t>
         </is>
       </c>
     </row>
@@ -7755,9 +7739,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F228" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9457（1/3）</t>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>0.9511 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7787,9 +7771,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F229" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>0.9511 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7819,9 +7803,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F230" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>0.9511 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7851,9 +7835,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F231" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>0.9512 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -7883,9 +7867,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -7915,9 +7899,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>运行中（0/3）</t>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -7947,9 +7931,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F234" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -7979,9 +7963,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F235" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0038</t>
         </is>
       </c>
     </row>
@@ -8011,9 +7995,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F236" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0037</t>
         </is>
       </c>
     </row>
@@ -8043,9 +8027,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F237" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>0.9572 ± 0.0029</t>
         </is>
       </c>
     </row>
@@ -8075,9 +8059,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F238" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>0.9582 ± 0.0051</t>
         </is>
       </c>
     </row>
@@ -8107,9 +8091,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F239" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0038</t>
         </is>
       </c>
     </row>
@@ -8139,9 +8123,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F240" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>0.9572 ± 0.0031</t>
         </is>
       </c>
     </row>
@@ -8171,9 +8155,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F241" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>0.9583 ± 0.0054</t>
         </is>
       </c>
     </row>
@@ -8203,9 +8187,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -8235,9 +8219,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F243" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>0.9572 ± 0.0031</t>
         </is>
       </c>
     </row>
@@ -8267,9 +8251,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F244" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>0.9584 ± 0.0054</t>
         </is>
       </c>
     </row>
@@ -8299,9 +8283,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F245" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>0.9547</t>
         </is>
       </c>
     </row>
@@ -8331,9 +8315,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F246" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>0.9547</t>
         </is>
       </c>
     </row>
@@ -8363,9 +8347,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F247" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>0.9741</t>
         </is>
       </c>
     </row>
@@ -8395,9 +8379,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F248" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>0.9741</t>
         </is>
       </c>
     </row>
@@ -8427,9 +8411,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F249" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>0.9741</t>
         </is>
       </c>
     </row>
@@ -8459,9 +8443,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F250" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>0.9750</t>
         </is>
       </c>
     </row>
@@ -8491,9 +8475,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F251" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>0.9751</t>
         </is>
       </c>
     </row>
@@ -8523,9 +8507,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F252" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>0.9524</t>
         </is>
       </c>
     </row>
@@ -8555,9 +8539,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F253" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>0.9089</t>
         </is>
       </c>
     </row>
@@ -8587,9 +8571,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F254" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>0.9547</t>
         </is>
       </c>
     </row>
@@ -8619,9 +8603,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F255" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>0.9547</t>
         </is>
       </c>
     </row>
@@ -8651,9 +8635,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F256" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>0.9741</t>
         </is>
       </c>
     </row>
@@ -8683,9 +8667,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F257" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>0.9741</t>
         </is>
       </c>
     </row>
@@ -8715,9 +8699,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F258" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>0.9741</t>
         </is>
       </c>
     </row>
@@ -8747,9 +8731,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F259" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>0.9750</t>
         </is>
       </c>
     </row>
@@ -8779,9 +8763,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F260" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>0.9751</t>
         </is>
       </c>
     </row>
@@ -8811,9 +8795,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F261" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>0.9524</t>
         </is>
       </c>
     </row>
@@ -8843,9 +8827,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F262" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>0.9089</t>
         </is>
       </c>
     </row>
@@ -8875,9 +8859,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -8907,9 +8891,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>运行中（0/3）</t>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -8939,9 +8923,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F265" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -8971,9 +8955,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F266" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0038</t>
         </is>
       </c>
     </row>
@@ -9003,9 +8987,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -9035,9 +9019,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F268" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -9067,9 +9051,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F269" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -9099,9 +9083,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F270" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0038</t>
         </is>
       </c>
     </row>
@@ -9131,9 +9115,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F271" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>0.9570 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -9163,9 +9147,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F272" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>0.9598 ± 0.0033</t>
         </is>
       </c>
     </row>
@@ -9259,9 +9243,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F275" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -9291,9 +9275,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9555（2/3）</t>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>0.9569 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -9323,9 +9307,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F277" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>0.9584 ± 0.0017</t>
         </is>
       </c>
     </row>
@@ -9355,9 +9339,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F278" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>0.9593 ± 0.0019</t>
         </is>
       </c>
     </row>
@@ -9387,9 +9371,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F279" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>0.9578 ± 0.0022</t>
         </is>
       </c>
     </row>
@@ -9419,9 +9403,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F280" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>0.9720 ± 0.0037</t>
         </is>
       </c>
     </row>
@@ -9451,9 +9435,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F281" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>0.9601 ± 0.0043</t>
         </is>
       </c>
     </row>
@@ -9483,9 +9467,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F282" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -9515,9 +9499,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F283" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>0.9908 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -9547,9 +9531,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F284" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>0.9891 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -9579,9 +9563,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F285" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -9611,9 +9595,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F286" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -9643,9 +9627,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F287" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -9675,9 +9659,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F288" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -9707,9 +9691,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F289" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>0.9908 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -9739,9 +9723,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F290" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>0.9908 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -9771,9 +9755,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F291" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>0.9908 ± 0.0010</t>
         </is>
       </c>
     </row>
@@ -9803,9 +9787,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F292" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>0.9891 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -9835,9 +9819,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F293" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>0.9891 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -9867,9 +9851,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F294" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>0.9890 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -9899,9 +9883,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F295" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -9931,9 +9915,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F296" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -9963,9 +9947,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F297" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -9995,9 +9979,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F298" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -10027,9 +10011,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F299" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -10059,9 +10043,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F300" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -10091,9 +10075,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F301" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F301" s="3" t="inlineStr">
+        <is>
+          <t>0.9939 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -10123,9 +10107,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F302" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>0.9891 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -10155,9 +10139,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F303" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>0.9890 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -10187,9 +10171,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F304" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>0.9890 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -10219,9 +10203,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F305" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>0.9890 ± 0.0014</t>
         </is>
       </c>
     </row>
@@ -10251,9 +10235,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F306" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10283,9 +10267,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F307" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10315,9 +10299,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F308" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10347,9 +10331,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F309" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10379,9 +10363,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F310" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0005</t>
         </is>
       </c>
     </row>
@@ -10411,9 +10395,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F311" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>0.9920 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10443,9 +10427,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F312" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>0.9918 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -10475,9 +10459,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F313" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0005</t>
         </is>
       </c>
     </row>
@@ -10507,9 +10491,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F314" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>0.9920 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10539,9 +10523,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F315" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>0.9918 ± 0.0003</t>
         </is>
       </c>
     </row>
@@ -10571,9 +10555,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F316" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10603,9 +10587,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F317" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>0.9920 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -10635,9 +10619,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F318" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>0.9919 ± 0.0003</t>
         </is>
       </c>
     </row>
@@ -10667,9 +10651,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F319" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>0.9872</t>
         </is>
       </c>
     </row>
@@ -10699,9 +10683,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F320" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>0.9872</t>
         </is>
       </c>
     </row>
@@ -10731,9 +10715,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F321" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>0.9949</t>
         </is>
       </c>
     </row>
@@ -10763,9 +10747,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F322" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>0.9949</t>
         </is>
       </c>
     </row>
@@ -10795,9 +10779,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F323" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F323" s="3" t="inlineStr">
+        <is>
+          <t>0.9949</t>
         </is>
       </c>
     </row>
@@ -10827,9 +10811,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F324" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>0.9959</t>
         </is>
       </c>
     </row>
@@ -10859,9 +10843,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F325" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F325" s="3" t="inlineStr">
+        <is>
+          <t>0.9959</t>
         </is>
       </c>
     </row>
@@ -10891,9 +10875,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F326" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>0.9905</t>
         </is>
       </c>
     </row>
@@ -10923,9 +10907,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F327" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F327" s="3" t="inlineStr">
+        <is>
+          <t>0.9273</t>
         </is>
       </c>
     </row>
@@ -10955,9 +10939,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F328" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>0.9872</t>
         </is>
       </c>
     </row>
@@ -10987,9 +10971,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F329" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F329" s="3" t="inlineStr">
+        <is>
+          <t>0.9872</t>
         </is>
       </c>
     </row>
@@ -11019,9 +11003,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F330" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F330" s="3" t="inlineStr">
+        <is>
+          <t>0.9949</t>
         </is>
       </c>
     </row>
@@ -11051,9 +11035,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F331" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F331" s="3" t="inlineStr">
+        <is>
+          <t>0.9949</t>
         </is>
       </c>
     </row>
@@ -11083,9 +11067,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F332" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F332" s="3" t="inlineStr">
+        <is>
+          <t>0.9949</t>
         </is>
       </c>
     </row>
@@ -11115,9 +11099,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F333" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F333" s="3" t="inlineStr">
+        <is>
+          <t>0.9959</t>
         </is>
       </c>
     </row>
@@ -11147,9 +11131,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F334" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>0.9959</t>
         </is>
       </c>
     </row>
@@ -11179,9 +11163,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F335" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F335" s="3" t="inlineStr">
+        <is>
+          <t>0.9905</t>
         </is>
       </c>
     </row>
@@ -11211,9 +11195,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F336" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F336" s="3" t="inlineStr">
+        <is>
+          <t>0.9273</t>
         </is>
       </c>
     </row>
@@ -11243,9 +11227,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F337" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11275,9 +11259,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F338" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11307,9 +11291,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F339" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F339" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11339,9 +11323,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F340" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F340" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11371,9 +11355,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F341" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F341" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11403,9 +11387,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F342" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F342" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11435,9 +11419,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F343" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F343" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11467,9 +11451,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F344" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F344" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11499,9 +11483,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F345" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F345" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11531,9 +11515,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F346" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F346" s="3" t="inlineStr">
+        <is>
+          <t>0.9920 ± 0.0008</t>
         </is>
       </c>
     </row>
@@ -11627,9 +11611,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F349" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F349" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11659,9 +11643,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F350" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F350" s="3" t="inlineStr">
+        <is>
+          <t>0.9922 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11691,9 +11675,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F351" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F351" s="3" t="inlineStr">
+        <is>
+          <t>0.9932 ± 0.0004</t>
         </is>
       </c>
     </row>
@@ -11723,9 +11707,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F352" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F352" s="3" t="inlineStr">
+        <is>
+          <t>0.9884 ± 0.0019</t>
         </is>
       </c>
     </row>
@@ -11755,9 +11739,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F353" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F353" s="3" t="inlineStr">
+        <is>
+          <t>0.9919 ± 0.0012</t>
         </is>
       </c>
     </row>
@@ -11787,9 +11771,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F354" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F354" s="3" t="inlineStr">
+        <is>
+          <t>0.9947 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -11819,9 +11803,9 @@
           <t>AUC 最大化</t>
         </is>
       </c>
-      <c r="F355" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F355" s="3" t="inlineStr">
+        <is>
+          <t>0.9929 ± 0.0001</t>
         </is>
       </c>
     </row>
@@ -11851,9 +11835,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F356" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F356" s="3" t="inlineStr">
+        <is>
+          <t>0.8382 ± 0.0437</t>
         </is>
       </c>
     </row>
@@ -11883,9 +11867,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F357" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F357" s="3" t="inlineStr">
+        <is>
+          <t>0.8599 ± 0.0221</t>
         </is>
       </c>
     </row>
@@ -11915,9 +11899,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F358" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F358" s="3" t="inlineStr">
+        <is>
+          <t>0.8575 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -11947,9 +11931,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F359" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F359" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -11979,9 +11963,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F360" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F360" s="3" t="inlineStr">
+        <is>
+          <t>0.8454 ± 0.0042</t>
         </is>
       </c>
     </row>
@@ -12011,9 +11995,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F361" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F361" s="3" t="inlineStr">
+        <is>
+          <t>0.8237 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -12043,9 +12027,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F362" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F362" s="3" t="inlineStr">
+        <is>
+          <t>0.8116 ± 0.0261</t>
         </is>
       </c>
     </row>
@@ -12075,9 +12059,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F363" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F363" s="3" t="inlineStr">
+        <is>
+          <t>0.8599 ± 0.0084</t>
         </is>
       </c>
     </row>
@@ -12107,9 +12091,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F364" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F364" s="3" t="inlineStr">
+        <is>
+          <t>0.8430 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -12139,9 +12123,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F365" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F365" s="3" t="inlineStr">
+        <is>
+          <t>0.8406 ± 0.0332</t>
         </is>
       </c>
     </row>
@@ -12171,9 +12155,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F366" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F366" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -12203,9 +12187,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F367" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F367" s="3" t="inlineStr">
+        <is>
+          <t>0.8551 ± 0.0145</t>
         </is>
       </c>
     </row>
@@ -12235,9 +12219,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F368" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F368" s="3" t="inlineStr">
+        <is>
+          <t>0.8599 ± 0.0221</t>
         </is>
       </c>
     </row>
@@ -12267,9 +12251,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F369" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F369" s="3" t="inlineStr">
+        <is>
+          <t>0.3913</t>
         </is>
       </c>
     </row>
@@ -12299,9 +12283,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F370" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F370" s="3" t="inlineStr">
+        <is>
+          <t>0.4058</t>
         </is>
       </c>
     </row>
@@ -12331,9 +12315,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F371" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F371" s="3" t="inlineStr">
+        <is>
+          <t>0.6739</t>
         </is>
       </c>
     </row>
@@ -12363,9 +12347,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F372" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F372" s="3" t="inlineStr">
+        <is>
+          <t>0.5217</t>
         </is>
       </c>
     </row>
@@ -12395,9 +12379,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F373" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F373" s="3" t="inlineStr">
+        <is>
+          <t>0.4275</t>
         </is>
       </c>
     </row>
@@ -12427,9 +12411,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F374" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F374" s="3" t="inlineStr">
+        <is>
+          <t>0.8188</t>
         </is>
       </c>
     </row>
@@ -12459,9 +12443,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F375" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F375" s="3" t="inlineStr">
+        <is>
+          <t>0.8696</t>
         </is>
       </c>
     </row>
@@ -12491,9 +12475,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F376" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F376" s="3" t="inlineStr">
+        <is>
+          <t>0.8696</t>
         </is>
       </c>
     </row>
@@ -12523,9 +12507,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F377" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F377" s="3" t="inlineStr">
+        <is>
+          <t>0.4130</t>
         </is>
       </c>
     </row>
@@ -12555,9 +12539,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F378" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F378" s="3" t="inlineStr">
+        <is>
+          <t>0.3913</t>
         </is>
       </c>
     </row>
@@ -12587,9 +12571,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F379" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F379" s="3" t="inlineStr">
+        <is>
+          <t>0.4058</t>
         </is>
       </c>
     </row>
@@ -12619,9 +12603,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F380" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F380" s="3" t="inlineStr">
+        <is>
+          <t>0.6739</t>
         </is>
       </c>
     </row>
@@ -12651,9 +12635,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F381" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F381" s="3" t="inlineStr">
+        <is>
+          <t>0.5217</t>
         </is>
       </c>
     </row>
@@ -12683,9 +12667,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F382" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F382" s="3" t="inlineStr">
+        <is>
+          <t>0.4275</t>
         </is>
       </c>
     </row>
@@ -12715,9 +12699,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F383" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F383" s="3" t="inlineStr">
+        <is>
+          <t>0.8188</t>
         </is>
       </c>
     </row>
@@ -12747,9 +12731,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F384" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F384" s="3" t="inlineStr">
+        <is>
+          <t>0.8696</t>
         </is>
       </c>
     </row>
@@ -12779,9 +12763,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F385" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F385" s="3" t="inlineStr">
+        <is>
+          <t>0.8696</t>
         </is>
       </c>
     </row>
@@ -12811,9 +12795,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F386" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F386" s="3" t="inlineStr">
+        <is>
+          <t>0.4130</t>
         </is>
       </c>
     </row>
@@ -12843,9 +12827,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F387" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F387" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -12875,9 +12859,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F388" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F388" s="3" t="inlineStr">
+        <is>
+          <t>0.8889 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -12907,9 +12891,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F389" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F389" s="3" t="inlineStr">
+        <is>
+          <t>0.8696 ± 0.0145</t>
         </is>
       </c>
     </row>
@@ -12939,9 +12923,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F390" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F390" s="3" t="inlineStr">
+        <is>
+          <t>0.8865 ± 0.0084</t>
         </is>
       </c>
     </row>
@@ -12971,9 +12955,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F391" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F391" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -13003,9 +12987,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F392" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F392" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -13035,9 +13019,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F393" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F393" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -13067,9 +13051,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F394" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F394" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -13099,9 +13083,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F395" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F395" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -13131,9 +13115,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F396" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F396" s="3" t="inlineStr">
+        <is>
+          <t>0.8623 ± 0.0192</t>
         </is>
       </c>
     </row>
@@ -13163,9 +13147,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F397" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F397" s="3" t="inlineStr">
+        <is>
+          <t>0.8865 ± 0.0151</t>
         </is>
       </c>
     </row>
@@ -13195,9 +13179,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F398" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F398" s="3" t="inlineStr">
+        <is>
+          <t>0.6498 ± 0.0553</t>
         </is>
       </c>
     </row>
@@ -13227,9 +13211,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F399" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F399" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -13259,9 +13243,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F400" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F400" s="3" t="inlineStr">
+        <is>
+          <t>0.8671 ± 0.0182</t>
         </is>
       </c>
     </row>
@@ -13291,9 +13275,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F401" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F401" s="3" t="inlineStr">
+        <is>
+          <t>0.8599 ± 0.0399</t>
         </is>
       </c>
     </row>
@@ -13323,9 +13307,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F402" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F402" s="3" t="inlineStr">
+        <is>
+          <t>0.8333 ± 0.0126</t>
         </is>
       </c>
     </row>
@@ -13355,9 +13339,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F403" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F403" s="3" t="inlineStr">
+        <is>
+          <t>0.8188 ± 0.0126</t>
         </is>
       </c>
     </row>
@@ -13387,9 +13371,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F404" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F404" s="3" t="inlineStr">
+        <is>
+          <t>0.8140 ± 0.0167</t>
         </is>
       </c>
     </row>
@@ -13419,9 +13403,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F405" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F405" s="3" t="inlineStr">
+        <is>
+          <t>0.8599 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -13451,9 +13435,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F406" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F406" s="3" t="inlineStr">
+        <is>
+          <t>0.9513 ± 0.0152</t>
         </is>
       </c>
     </row>
@@ -13483,9 +13467,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F407" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F407" s="3" t="inlineStr">
+        <is>
+          <t>0.9367 ± 0.0042</t>
         </is>
       </c>
     </row>
@@ -13515,9 +13499,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F408" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F408" s="3" t="inlineStr">
+        <is>
+          <t>0.9367 ± 0.0169</t>
         </is>
       </c>
     </row>
@@ -13547,9 +13531,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F409" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F409" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -13579,9 +13563,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F410" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F410" s="3" t="inlineStr">
+        <is>
+          <t>0.9319 ± 0.0184</t>
         </is>
       </c>
     </row>
@@ -13611,9 +13595,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F411" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F411" s="3" t="inlineStr">
+        <is>
+          <t>0.9440 ± 0.0084</t>
         </is>
       </c>
     </row>
@@ -13643,9 +13627,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F412" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F412" s="3" t="inlineStr">
+        <is>
+          <t>0.9343 ± 0.0126</t>
         </is>
       </c>
     </row>
@@ -13675,9 +13659,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F413" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F413" s="3" t="inlineStr">
+        <is>
+          <t>0.9367 ± 0.0152</t>
         </is>
       </c>
     </row>
@@ -13707,9 +13691,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F414" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F414" s="3" t="inlineStr">
+        <is>
+          <t>0.9538 ± 0.0042</t>
         </is>
       </c>
     </row>
@@ -13739,9 +13723,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F415" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F415" s="3" t="inlineStr">
+        <is>
+          <t>0.9367 ± 0.0042</t>
         </is>
       </c>
     </row>
@@ -13771,9 +13755,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F416" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F416" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -13803,9 +13787,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F417" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F417" s="3" t="inlineStr">
+        <is>
+          <t>0.9538 ± 0.0042</t>
         </is>
       </c>
     </row>
@@ -13835,9 +13819,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F418" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F418" s="3" t="inlineStr">
+        <is>
+          <t>0.9416 ± 0.0000</t>
         </is>
       </c>
     </row>
@@ -13867,9 +13851,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F419" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F419" s="3" t="inlineStr">
+        <is>
+          <t>0.8467</t>
         </is>
       </c>
     </row>
@@ -13899,9 +13883,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F420" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F420" s="3" t="inlineStr">
+        <is>
+          <t>0.8394</t>
         </is>
       </c>
     </row>
@@ -13931,9 +13915,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F421" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F421" s="3" t="inlineStr">
+        <is>
+          <t>0.9124</t>
         </is>
       </c>
     </row>
@@ -13963,9 +13947,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F422" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F422" s="3" t="inlineStr">
+        <is>
+          <t>0.8978</t>
         </is>
       </c>
     </row>
@@ -13995,9 +13979,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F423" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F423" s="3" t="inlineStr">
+        <is>
+          <t>0.9197</t>
         </is>
       </c>
     </row>
@@ -14027,9 +14011,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F424" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F424" s="3" t="inlineStr">
+        <is>
+          <t>0.9416</t>
         </is>
       </c>
     </row>
@@ -14059,9 +14043,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F425" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F425" s="3" t="inlineStr">
+        <is>
+          <t>0.9343</t>
         </is>
       </c>
     </row>
@@ -14091,9 +14075,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F426" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F426" s="3" t="inlineStr">
+        <is>
+          <t>0.9489</t>
         </is>
       </c>
     </row>
@@ -14123,9 +14107,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F427" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F427" s="3" t="inlineStr">
+        <is>
+          <t>0.7810</t>
         </is>
       </c>
     </row>
@@ -14155,9 +14139,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F428" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F428" s="3" t="inlineStr">
+        <is>
+          <t>0.8467</t>
         </is>
       </c>
     </row>
@@ -14187,9 +14171,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F429" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F429" s="3" t="inlineStr">
+        <is>
+          <t>0.8394</t>
         </is>
       </c>
     </row>
@@ -14219,9 +14203,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F430" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F430" s="3" t="inlineStr">
+        <is>
+          <t>0.9124</t>
         </is>
       </c>
     </row>
@@ -14251,9 +14235,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F431" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F431" s="3" t="inlineStr">
+        <is>
+          <t>0.8978</t>
         </is>
       </c>
     </row>
@@ -14283,9 +14267,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F432" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F432" s="3" t="inlineStr">
+        <is>
+          <t>0.9197</t>
         </is>
       </c>
     </row>
@@ -14315,9 +14299,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F433" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F433" s="3" t="inlineStr">
+        <is>
+          <t>0.9416</t>
         </is>
       </c>
     </row>
@@ -14347,9 +14331,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F434" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F434" s="3" t="inlineStr">
+        <is>
+          <t>0.9343</t>
         </is>
       </c>
     </row>
@@ -14379,9 +14363,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F435" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F435" s="3" t="inlineStr">
+        <is>
+          <t>0.9489</t>
         </is>
       </c>
     </row>
@@ -14411,9 +14395,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F436" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F436" s="3" t="inlineStr">
+        <is>
+          <t>0.7810</t>
         </is>
       </c>
     </row>
@@ -14443,9 +14427,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F437" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F437" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14475,9 +14459,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F438" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F438" s="3" t="inlineStr">
+        <is>
+          <t>0.9416 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -14507,9 +14491,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F439" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F439" s="3" t="inlineStr">
+        <is>
+          <t>0.9416 ± 0.0146</t>
         </is>
       </c>
     </row>
@@ -14539,9 +14523,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F440" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F440" s="3" t="inlineStr">
+        <is>
+          <t>0.9416 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -14571,9 +14555,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F441" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F441" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14603,9 +14587,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F442" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F442" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14635,9 +14619,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F443" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F443" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14667,9 +14651,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F444" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F444" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14699,9 +14683,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F445" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F445" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14731,9 +14715,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F446" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F446" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0295</t>
         </is>
       </c>
     </row>
@@ -14763,9 +14747,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F447" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F447" s="3" t="inlineStr">
+        <is>
+          <t>0.9538 ± 0.0084</t>
         </is>
       </c>
     </row>
@@ -14795,9 +14779,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F448" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F448" s="3" t="inlineStr">
+        <is>
+          <t>0.8856 ± 0.0211</t>
         </is>
       </c>
     </row>
@@ -14827,9 +14811,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F449" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F449" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14859,9 +14843,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F450" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F450" s="3" t="inlineStr">
+        <is>
+          <t>0.9392 ± 0.0111</t>
         </is>
       </c>
     </row>
@@ -14891,9 +14875,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F451" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F451" s="3" t="inlineStr">
+        <is>
+          <t>0.9489 ± 0.0146</t>
         </is>
       </c>
     </row>
@@ -14923,9 +14907,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F452" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F452" s="3" t="inlineStr">
+        <is>
+          <t>0.9489 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -14955,9 +14939,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F453" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F453" s="3" t="inlineStr">
+        <is>
+          <t>0.9489 ± 0.0000</t>
         </is>
       </c>
     </row>
@@ -14987,9 +14971,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F454" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F454" s="3" t="inlineStr">
+        <is>
+          <t>0.9489 ± 0.0073</t>
         </is>
       </c>
     </row>
@@ -15019,9 +15003,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F455" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F455" s="3" t="inlineStr">
+        <is>
+          <t>0.9465 ± 0.0169</t>
         </is>
       </c>
     </row>
@@ -15051,9 +15035,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F456" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F456" s="3" t="inlineStr">
+        <is>
+          <t>0.8920 ± 0.0430</t>
         </is>
       </c>
     </row>
@@ -15083,9 +15067,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F457" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F457" s="3" t="inlineStr">
+        <is>
+          <t>0.8826 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -15115,9 +15099,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F458" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F458" s="3" t="inlineStr">
+        <is>
+          <t>0.8779 ± 0.0430</t>
         </is>
       </c>
     </row>
@@ -15147,9 +15131,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F459" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F459" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -15179,9 +15163,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F460" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F460" s="3" t="inlineStr">
+        <is>
+          <t>0.9155 ± 0.0563</t>
         </is>
       </c>
     </row>
@@ -15211,9 +15195,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F461" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F461" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0453</t>
         </is>
       </c>
     </row>
@@ -15243,9 +15227,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F462" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F462" s="3" t="inlineStr">
+        <is>
+          <t>0.9014 ± 0.0244</t>
         </is>
       </c>
     </row>
@@ -15275,9 +15259,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F463" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F463" s="3" t="inlineStr">
+        <is>
+          <t>0.9155 ± 0.0563</t>
         </is>
       </c>
     </row>
@@ -15307,9 +15291,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F464" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F464" s="3" t="inlineStr">
+        <is>
+          <t>0.9155 ± 0.0563</t>
         </is>
       </c>
     </row>
@@ -15339,9 +15323,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F465" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F465" s="3" t="inlineStr">
+        <is>
+          <t>0.9014 ± 0.0244</t>
         </is>
       </c>
     </row>
@@ -15371,9 +15355,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F466" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F466" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -15403,9 +15387,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F467" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F467" s="3" t="inlineStr">
+        <is>
+          <t>0.9202 ± 0.0453</t>
         </is>
       </c>
     </row>
@@ -15435,9 +15419,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F468" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F468" s="3" t="inlineStr">
+        <is>
+          <t>0.9014 ± 0.0373</t>
         </is>
       </c>
     </row>
@@ -15467,9 +15451,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F469" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F469" s="3" t="inlineStr">
+        <is>
+          <t>0.5211</t>
         </is>
       </c>
     </row>
@@ -15499,9 +15483,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F470" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F470" s="3" t="inlineStr">
+        <is>
+          <t>0.5352</t>
         </is>
       </c>
     </row>
@@ -15531,9 +15515,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F471" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F471" s="3" t="inlineStr">
+        <is>
+          <t>0.6056</t>
         </is>
       </c>
     </row>
@@ -15563,9 +15547,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F472" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F472" s="3" t="inlineStr">
+        <is>
+          <t>0.6901</t>
         </is>
       </c>
     </row>
@@ -15595,9 +15579,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F473" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F473" s="3" t="inlineStr">
+        <is>
+          <t>0.7042</t>
         </is>
       </c>
     </row>
@@ -15627,9 +15611,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F474" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F474" s="3" t="inlineStr">
+        <is>
+          <t>0.8028</t>
         </is>
       </c>
     </row>
@@ -15659,9 +15643,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F475" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F475" s="3" t="inlineStr">
+        <is>
+          <t>0.8169</t>
         </is>
       </c>
     </row>
@@ -15691,9 +15675,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F476" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F476" s="3" t="inlineStr">
+        <is>
+          <t>0.8592</t>
         </is>
       </c>
     </row>
@@ -15723,9 +15707,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F477" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F477" s="3" t="inlineStr">
+        <is>
+          <t>0.6479</t>
         </is>
       </c>
     </row>
@@ -15755,9 +15739,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F478" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F478" s="3" t="inlineStr">
+        <is>
+          <t>0.5211</t>
         </is>
       </c>
     </row>
@@ -15787,9 +15771,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F479" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F479" s="3" t="inlineStr">
+        <is>
+          <t>0.5352</t>
         </is>
       </c>
     </row>
@@ -15819,9 +15803,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F480" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F480" s="3" t="inlineStr">
+        <is>
+          <t>0.6056</t>
         </is>
       </c>
     </row>
@@ -15851,9 +15835,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F481" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F481" s="3" t="inlineStr">
+        <is>
+          <t>0.6901</t>
         </is>
       </c>
     </row>
@@ -15883,9 +15867,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F482" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F482" s="3" t="inlineStr">
+        <is>
+          <t>0.7042</t>
         </is>
       </c>
     </row>
@@ -15915,9 +15899,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F483" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>0.8028</t>
         </is>
       </c>
     </row>
@@ -15947,9 +15931,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F484" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F484" s="3" t="inlineStr">
+        <is>
+          <t>0.8169</t>
         </is>
       </c>
     </row>
@@ -15979,9 +15963,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F485" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F485" s="3" t="inlineStr">
+        <is>
+          <t>0.8592</t>
         </is>
       </c>
     </row>
@@ -16011,9 +15995,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F486" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F486" s="3" t="inlineStr">
+        <is>
+          <t>0.6479</t>
         </is>
       </c>
     </row>
@@ -16043,9 +16027,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F487" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F487" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16075,9 +16059,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F488" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F488" s="3" t="inlineStr">
+        <is>
+          <t>0.9155 ± 0.0423</t>
         </is>
       </c>
     </row>
@@ -16107,9 +16091,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F489" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F489" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16139,9 +16123,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F490" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F490" s="3" t="inlineStr">
+        <is>
+          <t>0.9108 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16171,9 +16155,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F491" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F491" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16203,9 +16187,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F492" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F492" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16235,9 +16219,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F493" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F493" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16267,9 +16251,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F494" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F494" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16299,9 +16283,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F495" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F495" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16331,9 +16315,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F496" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F496" s="3" t="inlineStr">
+        <is>
+          <t>0.9108 ± 0.0430</t>
         </is>
       </c>
     </row>
@@ -16363,9 +16347,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F497" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F497" s="3" t="inlineStr">
+        <is>
+          <t>0.9014 ± 0.0508</t>
         </is>
       </c>
     </row>
@@ -16395,9 +16379,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F498" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F498" s="3" t="inlineStr">
+        <is>
+          <t>0.6995 ± 0.0938</t>
         </is>
       </c>
     </row>
@@ -16427,9 +16411,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F499" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F499" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16459,9 +16443,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F500" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F500" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16491,9 +16475,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F501" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F501" s="3" t="inlineStr">
+        <is>
+          <t>0.9155 ± 0.0244</t>
         </is>
       </c>
     </row>
@@ -16523,9 +16507,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F502" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F502" s="3" t="inlineStr">
+        <is>
+          <t>0.8826 ± 0.0081</t>
         </is>
       </c>
     </row>
@@ -16555,9 +16539,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F503" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F503" s="3" t="inlineStr">
+        <is>
+          <t>0.9249 ± 0.0215</t>
         </is>
       </c>
     </row>
@@ -16587,9 +16571,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F504" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F504" s="3" t="inlineStr">
+        <is>
+          <t>0.9061 ± 0.0495</t>
         </is>
       </c>
     </row>
@@ -16619,9 +16603,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F505" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F505" s="3" t="inlineStr">
+        <is>
+          <t>0.9108 ± 0.0430</t>
         </is>
       </c>
     </row>
@@ -16651,9 +16635,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F506" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F506" s="3" t="inlineStr">
+        <is>
+          <t>0.9550 ± 0.0062</t>
         </is>
       </c>
     </row>
@@ -16683,9 +16667,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F507" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F507" s="3" t="inlineStr">
+        <is>
+          <t>0.9016 ± 0.0356</t>
         </is>
       </c>
     </row>
@@ -16715,9 +16699,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F508" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F508" s="3" t="inlineStr">
+        <is>
+          <t>0.8802 ± 0.0370</t>
         </is>
       </c>
     </row>
@@ -16747,9 +16731,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F509" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F509" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -16779,9 +16763,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F510" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F510" s="3" t="inlineStr">
+        <is>
+          <t>0.9550 ± 0.0062</t>
         </is>
       </c>
     </row>
@@ -16811,9 +16795,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F511" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F511" s="3" t="inlineStr">
+        <is>
+          <t>0.9550 ± 0.0062</t>
         </is>
       </c>
     </row>
@@ -16843,9 +16827,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F512" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F512" s="3" t="inlineStr">
+        <is>
+          <t>0.9550 ± 0.0062</t>
         </is>
       </c>
     </row>
@@ -16875,9 +16859,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F513" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F513" s="3" t="inlineStr">
+        <is>
+          <t>0.9016 ± 0.0356</t>
         </is>
       </c>
     </row>
@@ -16907,9 +16891,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F514" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F514" s="3" t="inlineStr">
+        <is>
+          <t>0.9016 ± 0.0356</t>
         </is>
       </c>
     </row>
@@ -16939,9 +16923,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F515" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F515" s="3" t="inlineStr">
+        <is>
+          <t>0.9016 ± 0.0356</t>
         </is>
       </c>
     </row>
@@ -16971,9 +16955,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F516" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F516" s="3" t="inlineStr">
+        <is>
+          <t>0.8802 ± 0.0370</t>
         </is>
       </c>
     </row>
@@ -17003,9 +16987,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F517" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F517" s="3" t="inlineStr">
+        <is>
+          <t>0.8802 ± 0.0370</t>
         </is>
       </c>
     </row>
@@ -17035,9 +17019,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F518" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F518" s="3" t="inlineStr">
+        <is>
+          <t>0.8802 ± 0.0370</t>
         </is>
       </c>
     </row>
@@ -17067,9 +17051,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F519" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F519" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -17099,9 +17083,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F520" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F520" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -17131,9 +17115,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F521" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F521" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -17163,9 +17147,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F522" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F522" s="3" t="inlineStr">
+        <is>
+          <t>0.9550 ± 0.0062</t>
         </is>
       </c>
     </row>
@@ -17195,9 +17179,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F523" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F523" s="3" t="inlineStr">
+        <is>
+          <t>0.9493 ± 0.0080</t>
         </is>
       </c>
     </row>
@@ -17227,9 +17211,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F524" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F524" s="3" t="inlineStr">
+        <is>
+          <t>0.9551 ± 0.0063</t>
         </is>
       </c>
     </row>
@@ -17259,9 +17243,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F525" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F525" s="3" t="inlineStr">
+        <is>
+          <t>0.9492 ± 0.0082</t>
         </is>
       </c>
     </row>
@@ -17291,9 +17275,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F526" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F526" s="3" t="inlineStr">
+        <is>
+          <t>0.8802 ± 0.0370</t>
         </is>
       </c>
     </row>
@@ -17323,9 +17307,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F527" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F527" s="3" t="inlineStr">
+        <is>
+          <t>0.8676 ± 0.0386</t>
         </is>
       </c>
     </row>
@@ -17355,9 +17339,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F528" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F528" s="3" t="inlineStr">
+        <is>
+          <t>0.8802 ± 0.0372</t>
         </is>
       </c>
     </row>
@@ -17387,9 +17371,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F529" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F529" s="3" t="inlineStr">
+        <is>
+          <t>0.8678 ± 0.0384</t>
         </is>
       </c>
     </row>
@@ -17419,9 +17403,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F530" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F530" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -17451,9 +17435,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F531" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F531" s="3" t="inlineStr">
+        <is>
+          <t>0.9187 ± 0.0235</t>
         </is>
       </c>
     </row>
@@ -17483,9 +17467,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F532" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F532" s="3" t="inlineStr">
+        <is>
+          <t>0.9243 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -17515,9 +17499,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F533" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F533" s="3" t="inlineStr">
+        <is>
+          <t>0.9187 ± 0.0235</t>
         </is>
       </c>
     </row>
@@ -17547,9 +17531,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F534" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F534" s="3" t="inlineStr">
+        <is>
+          <t>0.9420 ± 0.0081</t>
         </is>
       </c>
     </row>
@@ -17579,9 +17563,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F535" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F535" s="3" t="inlineStr">
+        <is>
+          <t>0.9437 ± 0.0103</t>
         </is>
       </c>
     </row>
@@ -17611,9 +17595,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F536" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F536" s="3" t="inlineStr">
+        <is>
+          <t>0.9138 ± 0.0299</t>
         </is>
       </c>
     </row>
@@ -17643,9 +17627,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F537" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F537" s="3" t="inlineStr">
+        <is>
+          <t>0.9312 ± 0.0143</t>
         </is>
       </c>
     </row>
@@ -17675,9 +17659,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F538" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F538" s="3" t="inlineStr">
+        <is>
+          <t>0.9399 ± 0.0109</t>
         </is>
       </c>
     </row>
@@ -17707,9 +17691,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F539" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F539" s="3" t="inlineStr">
+        <is>
+          <t>0.8989 ± 0.0401</t>
         </is>
       </c>
     </row>
@@ -17739,9 +17723,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F540" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F540" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -17771,9 +17755,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F541" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F541" s="3" t="inlineStr">
+        <is>
+          <t>0.9365 ± 0.0121</t>
         </is>
       </c>
     </row>
@@ -17803,9 +17787,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F542" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F542" s="3" t="inlineStr">
+        <is>
+          <t>0.8898 ± 0.0429</t>
         </is>
       </c>
     </row>
@@ -17835,9 +17819,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F543" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F543" s="3" t="inlineStr">
+        <is>
+          <t>0.6917</t>
         </is>
       </c>
     </row>
@@ -17867,9 +17851,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F544" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F544" s="3" t="inlineStr">
+        <is>
+          <t>0.6685</t>
         </is>
       </c>
     </row>
@@ -17899,9 +17883,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F545" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F545" s="3" t="inlineStr">
+        <is>
+          <t>0.8715</t>
         </is>
       </c>
     </row>
@@ -17931,9 +17915,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F546" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F546" s="3" t="inlineStr">
+        <is>
+          <t>0.7575</t>
         </is>
       </c>
     </row>
@@ -17963,9 +17947,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F547" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F547" s="3" t="inlineStr">
+        <is>
+          <t>0.6937</t>
         </is>
       </c>
     </row>
@@ -17995,9 +17979,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F548" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F548" s="3" t="inlineStr">
+        <is>
+          <t>0.9440</t>
         </is>
       </c>
     </row>
@@ -18027,9 +18011,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F549" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F549" s="3" t="inlineStr">
+        <is>
+          <t>0.9140</t>
         </is>
       </c>
     </row>
@@ -18059,9 +18043,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F550" s="5" t="inlineStr">
-        <is>
-          <t>运行中（0/1）</t>
+      <c r="F550" s="3" t="inlineStr">
+        <is>
+          <t>0.9525</t>
         </is>
       </c>
     </row>
@@ -18091,9 +18075,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F551" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F551" s="3" t="inlineStr">
+        <is>
+          <t>0.6625</t>
         </is>
       </c>
     </row>
@@ -18123,9 +18107,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F552" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F552" s="3" t="inlineStr">
+        <is>
+          <t>0.6917</t>
         </is>
       </c>
     </row>
@@ -18155,9 +18139,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F553" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F553" s="3" t="inlineStr">
+        <is>
+          <t>0.6685</t>
         </is>
       </c>
     </row>
@@ -18187,9 +18171,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F554" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F554" s="3" t="inlineStr">
+        <is>
+          <t>0.8715</t>
         </is>
       </c>
     </row>
@@ -18219,9 +18203,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F555" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F555" s="3" t="inlineStr">
+        <is>
+          <t>0.7575</t>
         </is>
       </c>
     </row>
@@ -18251,9 +18235,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F556" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F556" s="3" t="inlineStr">
+        <is>
+          <t>0.6937</t>
         </is>
       </c>
     </row>
@@ -18283,9 +18267,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F557" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F557" s="3" t="inlineStr">
+        <is>
+          <t>0.9440</t>
         </is>
       </c>
     </row>
@@ -18315,9 +18299,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F558" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F558" s="3" t="inlineStr">
+        <is>
+          <t>0.9140</t>
         </is>
       </c>
     </row>
@@ -18347,9 +18331,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F559" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F559" s="3" t="inlineStr">
+        <is>
+          <t>0.9525</t>
         </is>
       </c>
     </row>
@@ -18379,9 +18363,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F560" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/1）</t>
+      <c r="F560" s="3" t="inlineStr">
+        <is>
+          <t>0.6625</t>
         </is>
       </c>
     </row>
@@ -18411,9 +18395,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F561" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F561" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18443,9 +18427,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F562" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F562" s="3" t="inlineStr">
+        <is>
+          <t>0.9187 ± 0.0235</t>
         </is>
       </c>
     </row>
@@ -18475,9 +18459,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F563" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F563" s="3" t="inlineStr">
+        <is>
+          <t>0.9243 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18507,9 +18491,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F564" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F564" s="3" t="inlineStr">
+        <is>
+          <t>0.9187 ± 0.0235</t>
         </is>
       </c>
     </row>
@@ -18539,9 +18523,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F565" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F565" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18571,9 +18555,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F566" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F566" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18603,9 +18587,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F567" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F567" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18635,9 +18619,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F568" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F568" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18667,9 +18651,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F569" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F569" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18699,9 +18683,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F570" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F570" s="3" t="inlineStr">
+        <is>
+          <t>0.9268 ± 0.0164</t>
         </is>
       </c>
     </row>
@@ -18731,9 +18715,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F571" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.9457（2/3）</t>
+      <c r="F571" s="3" t="inlineStr">
+        <is>
+          <t>0.9480 ± 0.0061</t>
         </is>
       </c>
     </row>
@@ -18763,9 +18747,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F572" s="5" t="inlineStr">
-        <is>
-          <t>当前 0.6329（2/3）</t>
+      <c r="F572" s="3" t="inlineStr">
+        <is>
+          <t>0.7012 ± 0.1379</t>
         </is>
       </c>
     </row>
@@ -18795,9 +18779,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F573" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F573" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18827,9 +18811,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F574" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F574" s="3" t="inlineStr">
+        <is>
+          <t>0.9244 ± 0.0183</t>
         </is>
       </c>
     </row>
@@ -18859,9 +18843,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F575" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F575" s="3" t="inlineStr">
+        <is>
+          <t>0.9398 ± 0.0103</t>
         </is>
       </c>
     </row>
@@ -18891,9 +18875,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F576" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F576" s="3" t="inlineStr">
+        <is>
+          <t>0.7789 ± 0.0937</t>
         </is>
       </c>
     </row>
@@ -18923,9 +18907,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F577" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F577" s="3" t="inlineStr">
+        <is>
+          <t>0.8956 ± 0.0364</t>
         </is>
       </c>
     </row>
@@ -18955,9 +18939,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F578" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F578" s="3" t="inlineStr">
+        <is>
+          <t>0.9632 ± 0.0013</t>
         </is>
       </c>
     </row>
@@ -18987,9 +18971,9 @@
           <t>稳健分类</t>
         </is>
       </c>
-      <c r="F579" s="4" t="inlineStr">
-        <is>
-          <t>待运行（0/3）</t>
+      <c r="F579" s="3" t="inlineStr">
+        <is>
+          <t>0.9374 ± 0.0106</t>
         </is>
       </c>
     </row>
